--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62500.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62500.xlsx
@@ -705,9 +705,6 @@
       <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62500.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62500.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oykloy</t>
+          <t>Lsolu</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KYA</t>
+          <t>IKIEYAN</t>
         </is>
       </c>
     </row>
